--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.12489316231512</v>
+        <v>11.88279513887621</v>
       </c>
       <c r="D2" t="n">
-        <v>61.23104040143345</v>
+        <v>9.950044065232936</v>
       </c>
       <c r="E2" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F2" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.93543034850199</v>
+        <v>9.902007431631574</v>
       </c>
       <c r="D3" t="n">
-        <v>47.43370490058346</v>
+        <v>7.707977046344813</v>
       </c>
       <c r="E3" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F3" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.6236155146875</v>
+        <v>8.388837521136718</v>
       </c>
       <c r="D4" t="n">
-        <v>36.31294020123632</v>
+        <v>5.900852782700902</v>
       </c>
       <c r="E4" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F4" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.95600059307584</v>
+        <v>8.767850096374824</v>
       </c>
       <c r="D5" t="n">
-        <v>43.46960979015848</v>
+        <v>7.063811590900754</v>
       </c>
       <c r="E5" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F5" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.42548732187356</v>
+        <v>4.619141689804453</v>
       </c>
       <c r="D6" t="n">
-        <v>4.861558313862154</v>
+        <v>0.7900032260026</v>
       </c>
       <c r="E6" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F6" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>77.84624993197951</v>
+        <v>12.65001561394667</v>
       </c>
       <c r="D7" t="n">
-        <v>68.87770968040313</v>
+        <v>11.19262782306551</v>
       </c>
       <c r="E7" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F7" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.33565257613588</v>
+        <v>5.254543543622081</v>
       </c>
       <c r="D8" t="n">
-        <v>24.46307189495431</v>
+        <v>3.975249182930076</v>
       </c>
       <c r="E8" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F8" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>69.24874599371924</v>
+        <v>11.25292122397938</v>
       </c>
       <c r="D9" t="n">
-        <v>61.73223476067764</v>
+        <v>10.03148814861012</v>
       </c>
       <c r="E9" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F9" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>62.5</v>
+        <v>10.15625</v>
       </c>
       <c r="D10" t="n">
-        <v>55.91511423577708</v>
+        <v>9.086206063313774</v>
       </c>
       <c r="E10" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F10" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.95093414953337</v>
+        <v>3.242026799299173</v>
       </c>
       <c r="D11" t="n">
-        <v>16.4679660698637</v>
+        <v>2.676044486352851</v>
       </c>
       <c r="E11" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F11" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.63078946776307</v>
+        <v>8.552503288511499</v>
       </c>
       <c r="D12" t="n">
-        <v>46.19794367718113</v>
+        <v>7.507165847541934</v>
       </c>
       <c r="E12" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F12" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.62214450449026</v>
+        <v>4.001098481979668</v>
       </c>
       <c r="D13" t="n">
-        <v>17.46424919657298</v>
+        <v>2.837940494443109</v>
       </c>
       <c r="E13" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F13" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6.800735254367722</v>
+        <v>1.105119478834755</v>
       </c>
       <c r="D14" t="n">
-        <v>1.58113883008419</v>
+        <v>0.2569350598886809</v>
       </c>
       <c r="E14" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F14" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.97461981168406</v>
+        <v>3.08337571939866</v>
       </c>
       <c r="D15" t="n">
-        <v>24.76096302861664</v>
+        <v>4.023656492150205</v>
       </c>
       <c r="E15" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F15" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>27.742509435145</v>
+        <v>4.508157783211063</v>
       </c>
       <c r="D16" t="n">
-        <v>20.02248673104756</v>
+        <v>3.253654093795229</v>
       </c>
       <c r="E16" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F16" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>45.63441683641854</v>
+        <v>7.415592735918013</v>
       </c>
       <c r="D17" t="n">
-        <v>40.02811511925087</v>
+        <v>6.504568706878267</v>
       </c>
       <c r="E17" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F17" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.34301818504865</v>
+        <v>3.305740455070405</v>
       </c>
       <c r="D18" t="n">
-        <v>22.81077233688051</v>
+        <v>3.706750504743083</v>
       </c>
       <c r="E18" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F18" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>60.23768387834793</v>
+        <v>9.788623630231539</v>
       </c>
       <c r="D19" t="n">
-        <v>54.80943707393018</v>
+        <v>8.906533524513653</v>
       </c>
       <c r="E19" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F19" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>18.06239186818844</v>
+        <v>2.935138678580622</v>
       </c>
       <c r="D20" t="n">
-        <v>14.08900280360537</v>
+        <v>2.289462955585873</v>
       </c>
       <c r="E20" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F20" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>73.12361952646744</v>
+        <v>11.88258817305096</v>
       </c>
       <c r="D21" t="n">
-        <v>67.76850661928685</v>
+        <v>11.01238232563411</v>
       </c>
       <c r="E21" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F21" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>26.74415824063266</v>
+        <v>4.345925714102808</v>
       </c>
       <c r="D22" t="n">
-        <v>24.30020576044573</v>
+        <v>3.948783436072432</v>
       </c>
       <c r="E22" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F22" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>31.03648674786125</v>
+        <v>5.043429096527453</v>
       </c>
       <c r="D23" t="n">
-        <v>28.14154727215176</v>
+        <v>4.573001431724661</v>
       </c>
       <c r="E23" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F23" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>71.72467318151966</v>
+        <v>11.65525939199695</v>
       </c>
       <c r="D24" t="n">
-        <v>68.78460519843715</v>
+        <v>11.17749834474604</v>
       </c>
       <c r="E24" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F24" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>61.44920880707122</v>
+        <v>9.985496431149073</v>
       </c>
       <c r="D25" t="n">
-        <v>58.33095233235953</v>
+        <v>9.478779754008423</v>
       </c>
       <c r="E25" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F25" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>13.35943522429548</v>
+        <v>2.170908223948015</v>
       </c>
       <c r="D26" t="n">
-        <v>9.419101998687786</v>
+        <v>1.530604074786765</v>
       </c>
       <c r="E26" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F26" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>35.61552838164558</v>
+        <v>5.787523362017407</v>
       </c>
       <c r="D27" t="n">
-        <v>22.8972303002343</v>
+        <v>3.720799923788074</v>
       </c>
       <c r="E27" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F27" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>61.76415993411758</v>
+        <v>10.03667598929411</v>
       </c>
       <c r="D28" t="n">
-        <v>58.43179411775766</v>
+        <v>9.495166544135619</v>
       </c>
       <c r="E28" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F28" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>29.29226666677227</v>
+        <v>4.759993333350494</v>
       </c>
       <c r="D29" t="n">
-        <v>32.90083024983981</v>
+        <v>5.34638491559897</v>
       </c>
       <c r="E29" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F29" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>34.73406355101658</v>
+        <v>5.644285327040195</v>
       </c>
       <c r="D30" t="n">
-        <v>5.586284726598094</v>
+        <v>0.9077712680721902</v>
       </c>
       <c r="E30" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F30" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>27.71534580036987</v>
+        <v>4.503743692560104</v>
       </c>
       <c r="D31" t="n">
-        <v>6.28019677296501</v>
+        <v>1.020531975606814</v>
       </c>
       <c r="E31" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F31" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>65.7416664709524</v>
+        <v>10.68302080152976</v>
       </c>
       <c r="D32" t="n">
-        <v>56.54234306048444</v>
+        <v>9.188130747328723</v>
       </c>
       <c r="E32" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F32" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>48.52765667900457</v>
+        <v>7.885744210338244</v>
       </c>
       <c r="D33" t="n">
-        <v>45.2840248838591</v>
+        <v>7.358654043627104</v>
       </c>
       <c r="E33" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F33" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>59.01187014233994</v>
+        <v>9.58942889813024</v>
       </c>
       <c r="D34" t="n">
-        <v>48.86664308343946</v>
+        <v>7.940829501058912</v>
       </c>
       <c r="E34" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F34" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>16.37006576664812</v>
+        <v>2.660135687080319</v>
       </c>
       <c r="D35" t="n">
-        <v>12.34234854367614</v>
+        <v>2.005631638347373</v>
       </c>
       <c r="E35" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F35" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>29.10118207657001</v>
+        <v>4.728942087442626</v>
       </c>
       <c r="D36" t="n">
-        <v>32.55612895227789</v>
+        <v>5.290370954745157</v>
       </c>
       <c r="E36" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F36" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>17.48796422408706</v>
+        <v>2.841794186414147</v>
       </c>
       <c r="D37" t="n">
-        <v>20.83218244745802</v>
+        <v>3.385229647711928</v>
       </c>
       <c r="E37" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F37" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>21.20957034176884</v>
+        <v>3.446555180537436</v>
       </c>
       <c r="D38" t="n">
-        <v>13.1546946499289</v>
+        <v>2.137637880613447</v>
       </c>
       <c r="E38" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F38" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>53.91485859101022</v>
+        <v>8.761164521039161</v>
       </c>
       <c r="D39" t="n">
-        <v>40.78883559596381</v>
+        <v>6.62818578434412</v>
       </c>
       <c r="E39" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F39" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>39.63420242752029</v>
+        <v>6.440557894472048</v>
       </c>
       <c r="D40" t="n">
-        <v>18.5734929555628</v>
+        <v>3.018192605278954</v>
       </c>
       <c r="E40" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F40" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>23.1393808849242</v>
+        <v>3.760149393800182</v>
       </c>
       <c r="D41" t="n">
-        <v>22.42749899571815</v>
+        <v>3.644468586804199</v>
       </c>
       <c r="E41" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F41" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>65.65605854010674</v>
+        <v>10.66910951276735</v>
       </c>
       <c r="D42" t="n">
-        <v>47.1338013683774</v>
+        <v>7.659242722361327</v>
       </c>
       <c r="E42" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F42" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>16.66565090959008</v>
+        <v>2.708168272808389</v>
       </c>
       <c r="D43" t="n">
-        <v>18.42487621847559</v>
+        <v>2.994042385502283</v>
       </c>
       <c r="E43" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F43" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>79.51237904303544</v>
+        <v>12.92076159449326</v>
       </c>
       <c r="D44" t="n">
-        <v>57.66231443060614</v>
+        <v>9.370126094973498</v>
       </c>
       <c r="E44" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F44" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>31.23085197430797</v>
+        <v>5.075013445825046</v>
       </c>
       <c r="D45" t="n">
-        <v>15.32315335950043</v>
+        <v>2.490012420918821</v>
       </c>
       <c r="E45" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F45" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>24.66676714708844</v>
+        <v>4.008349661401872</v>
       </c>
       <c r="D46" t="n">
-        <v>10.48564763113184</v>
+        <v>1.703917740058924</v>
       </c>
       <c r="E46" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F46" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>18.19392371844808</v>
+        <v>2.956512604247814</v>
       </c>
       <c r="D47" t="n">
-        <v>14.71925225485946</v>
+        <v>2.391878491414663</v>
       </c>
       <c r="E47" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F47" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>64.89319964649658</v>
+        <v>10.54514494255569</v>
       </c>
       <c r="D48" t="n">
-        <v>40.31677713906247</v>
+        <v>6.551476285097652</v>
       </c>
       <c r="E48" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F48" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>41.29498150416973</v>
+        <v>6.710434494427581</v>
       </c>
       <c r="D49" t="n">
-        <v>15.04300060351906</v>
+        <v>2.444487598071847</v>
       </c>
       <c r="E49" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F49" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>27.79425253779802</v>
+        <v>4.516566037392179</v>
       </c>
       <c r="D50" t="n">
-        <v>13.72953021774598</v>
+        <v>2.231048660383722</v>
       </c>
       <c r="E50" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F50" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>38.9282060605241</v>
+        <v>6.325833484835167</v>
       </c>
       <c r="D51" t="n">
-        <v>5.590408597697029</v>
+        <v>0.9084413971257672</v>
       </c>
       <c r="E51" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F51" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>54.21575257723417</v>
+        <v>8.810059793800553</v>
       </c>
       <c r="D52" t="n">
-        <v>23.25888247023729</v>
+        <v>3.77956840141356</v>
       </c>
       <c r="E52" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F52" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>35.0470556554621</v>
+        <v>5.695146544012592</v>
       </c>
       <c r="D53" t="n">
-        <v>14.40555448429528</v>
+        <v>2.340902603697983</v>
       </c>
       <c r="E53" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F53" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>27.0555321614714</v>
+        <v>4.396523976239103</v>
       </c>
       <c r="D54" t="n">
-        <v>12.78022832113853</v>
+        <v>2.076787102185012</v>
       </c>
       <c r="E54" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F54" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>71.93124042105782</v>
+        <v>11.6888265684219</v>
       </c>
       <c r="D55" t="n">
-        <v>41.74896720332521</v>
+        <v>6.784207170540347</v>
       </c>
       <c r="E55" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F55" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>34.0310658891031</v>
+        <v>5.530048206979255</v>
       </c>
       <c r="D56" t="n">
-        <v>4.301162633521313</v>
+        <v>0.6989389279472135</v>
       </c>
       <c r="E56" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F56" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>44.98453290115097</v>
+        <v>7.309986596437033</v>
       </c>
       <c r="D57" t="n">
-        <v>10.18623641512737</v>
+        <v>1.655263417458198</v>
       </c>
       <c r="E57" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F57" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>73.34676131360146</v>
+        <v>11.91884871346024</v>
       </c>
       <c r="D58" t="n">
-        <v>38.4505036441226</v>
+        <v>6.248206842169923</v>
       </c>
       <c r="E58" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F58" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>81.73148856401157</v>
+        <v>13.28136689165188</v>
       </c>
       <c r="D59" t="n">
-        <v>34.31361893540879</v>
+        <v>5.575963077003928</v>
       </c>
       <c r="E59" t="n">
-        <v>20.47186936266335</v>
+        <v>3.326678771432795</v>
       </c>
       <c r="F59" t="n">
-        <v>19.2413759790311</v>
+        <v>3.126723596592554</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
